--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8</f>
+              <f>'30日跟踪'!$A$8:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8</f>
+              <f>'30日跟踪'!$D$8:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="7">
@@ -708,6 +708,26 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>第1/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>14.39000034332275</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-6.860838051963714</v>
+      </c>
+      <c r="D9" s="6">
+        <f>B9/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>第2/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$9</f>
+              <f>'30日跟踪'!$A$8:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$9</f>
+              <f>'30日跟踪'!$D$8:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="7">
@@ -728,6 +728,26 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>第2/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>13.77000045776367</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-4.308546704425719</v>
+      </c>
+      <c r="D10" s="6">
+        <f>B10/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>第3/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$10</f>
+              <f>'30日跟踪'!$A$8:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$10</f>
+              <f>'30日跟踪'!$D$8:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="7">
@@ -748,6 +748,26 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>第3/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>13.71000003814697</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-0.4357328803345828</v>
+      </c>
+      <c r="D11" s="6">
+        <f>B11/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>第4/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$11</f>
+              <f>'30日跟踪'!$A$8:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$11</f>
+              <f>'30日跟踪'!$D$8:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="7">
@@ -768,6 +768,26 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>第4/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>13.07999992370605</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-4.595186817563768</v>
+      </c>
+      <c r="D12" s="6">
+        <f>B12/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>第5/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$12</f>
+              <f>'30日跟踪'!$A$8:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$12</f>
+              <f>'30日跟踪'!$D$8:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="7">
@@ -788,6 +788,26 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>第5/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>12.72000026702881</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-2.752290969243709</v>
+      </c>
+      <c r="D13" s="6">
+        <f>B13/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>第6/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$13</f>
+              <f>'30日跟踪'!$A$8:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$13</f>
+              <f>'30日跟踪'!$D$8:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="7">
@@ -808,6 +808,26 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>第6/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>11.64000034332275</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-8.490565259699679</v>
+      </c>
+      <c r="D14" s="6">
+        <f>B14/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>第7/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$14</f>
+              <f>'30日跟踪'!$A$8:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$14</f>
+              <f>'30日跟踪'!$D$8:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="7">
@@ -828,6 +828,46 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>第7/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>11.44999980926514</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-1.632306945477113</v>
+      </c>
+      <c r="D15" s="6">
+        <f>B15/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>第8/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>10.35999965667725</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-9.519652146246171</v>
+      </c>
+      <c r="D16" s="6">
+        <f>B16/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>第9/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$16</f>
+              <f>'30日跟踪'!$A$8:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$16</f>
+              <f>'30日跟踪'!$D$8:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="7">
@@ -868,6 +868,26 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>第9/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>10.53999996185303</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1.737454740741873</v>
+      </c>
+      <c r="D17" s="6">
+        <f>B17/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>第10/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$17</f>
+              <f>'30日跟踪'!$A$8:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$17</f>
+              <f>'30日跟踪'!$D$8:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="7">
@@ -888,6 +888,26 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>第10/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>10.73999977111816</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1.897531404070096</v>
+      </c>
+      <c r="D18" s="6">
+        <f>B18/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>第11/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$18</f>
+              <f>'30日跟踪'!$A$8:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$18</f>
+              <f>'30日跟踪'!$D$8:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="7">
@@ -908,6 +908,26 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>第11/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>10.89000034332275</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1.396653402246506</v>
+      </c>
+      <c r="D19" s="6">
+        <f>B19/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>第12/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$19</f>
+              <f>'30日跟踪'!$A$8:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$19</f>
+              <f>'30日跟踪'!$D$8:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="7">
@@ -928,6 +928,26 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>第12/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>10.63000011444092</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-2.387513504912386</v>
+      </c>
+      <c r="D20" s="6">
+        <f>B20/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>第13/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$20</f>
+              <f>'30日跟踪'!$A$8:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$20</f>
+              <f>'30日跟踪'!$D$8:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="7">
@@ -948,6 +948,26 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>第13/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>10.60000038146973</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-0.2822176166342283</v>
+      </c>
+      <c r="D21" s="6">
+        <f>B21/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>第14/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$21</f>
+              <f>'30日跟踪'!$A$8:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$21</f>
+              <f>'30日跟踪'!$D$8:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="7">
@@ -968,6 +968,26 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>第14/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>10.6899995803833</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0.8490490157991415</v>
+      </c>
+      <c r="D22" s="6">
+        <f>B22/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>第15/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$22</f>
+              <f>'30日跟踪'!$A$8:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$22</f>
+              <f>'30日跟踪'!$D$8:$D$23</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="7">
@@ -988,6 +988,26 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>第15/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>11.53999996185303</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>7.951360288446785</v>
+      </c>
+      <c r="D23" s="6">
+        <f>B23/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>第16/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$23</f>
+              <f>'30日跟踪'!$A$8:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$23</f>
+              <f>'30日跟踪'!$D$8:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="7">
@@ -1008,6 +1008,26 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>第16/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>11.53999996185303</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6">
+        <f>B24/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>第17/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/XE_1_20261006.xlsx
+++ b/data/CROSS/EXCLE/XE_1_20261006.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$24</f>
+              <f>'30日跟踪'!$A$8:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$24</f>
+              <f>'30日跟踪'!$D$8:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="7">
@@ -1028,6 +1028,26 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>第17/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>11.69999980926514</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1.386480484757446</v>
+      </c>
+      <c r="D25" s="6">
+        <f>B25/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>第18/30个交易日</t>
         </is>
       </c>
     </row>
